--- a/SGC-CKN/Excel/77d75731-b6ce-40cf-8760-7f97e785ecd1_Thanh_Hoá_P1-120_D800_03-04-2026.xlsx
+++ b/SGC-CKN/Excel/77d75731-b6ce-40cf-8760-7f97e785ecd1_Thanh_Hoá_P1-120_D800_03-04-2026.xlsx
@@ -384,12 +384,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9F99D"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD9F99D"/>
       </patternFill>
     </fill>
     <fill>
@@ -557,17 +557,17 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1252,16 +1252,16 @@
         <v>-5.91</v>
       </c>
       <c r="G13" s="12">
-        <v>-9.22</v>
+        <v>-9.2</v>
       </c>
       <c r="H13" s="12">
         <v>0.23</v>
       </c>
       <c r="I13" s="12">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="J13" s="8">
-        <v>14.19</v>
+        <v>14.1</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1284,7 +1284,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="15">
-        <v>-9.22</v>
+        <v>-9.2</v>
       </c>
       <c r="G14" s="15">
         <v>-12.32</v>
@@ -1293,10 +1293,10 @@
         <v>0.48</v>
       </c>
       <c r="I14" s="15">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="J14" s="8">
-        <v>6.41</v>
+        <v>6.46</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1322,53 +1322,53 @@
         <v>-12.32</v>
       </c>
       <c r="G15" s="18">
-        <v>21.33</v>
+        <v>-21.33</v>
       </c>
       <c r="H15" s="18">
         <v>1.98</v>
       </c>
       <c r="I15" s="18">
-        <v>33.65</v>
-      </c>
-      <c r="J15" s="8">
-        <v>16.97</v>
+        <v>9.01</v>
+      </c>
+      <c r="J15" s="21">
+        <v>4.54</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="22">
         <v>-21.33</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="22">
         <v>-25.14</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="22">
         <v>0.98</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="22">
         <v>3.81</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="21">
         <v>3.87</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="23" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1427,16 +1427,16 @@
         <v>-39.3</v>
       </c>
       <c r="G18" s="28">
-        <v>-49.47</v>
+        <v>-44.47</v>
       </c>
       <c r="H18" s="28">
         <v>2.65</v>
       </c>
       <c r="I18" s="28">
-        <v>10.17</v>
-      </c>
-      <c r="J18" s="24">
-        <v>3.84</v>
+        <v>5.17</v>
+      </c>
+      <c r="J18" s="21">
+        <v>1.95</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>60</v>
@@ -1652,16 +1652,16 @@
         <v>-5.91</v>
       </c>
       <c r="F4" s="12">
-        <v>-9.22</v>
+        <v>-9.2</v>
       </c>
       <c r="G4" s="12">
         <v>0.23</v>
       </c>
       <c r="H4" s="12">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="I4" s="8">
-        <v>14.19</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-9.22</v>
+        <v>-9.2</v>
       </c>
       <c r="F5" s="15">
         <v>-12.32</v>
@@ -1687,10 +1687,10 @@
         <v>0.48</v>
       </c>
       <c r="H5" s="15">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="I5" s="8">
-        <v>6.41</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1710,44 +1710,44 @@
         <v>-12.32</v>
       </c>
       <c r="F6" s="18">
-        <v>21.33</v>
+        <v>-21.33</v>
       </c>
       <c r="G6" s="18">
         <v>1.98</v>
       </c>
       <c r="H6" s="18">
-        <v>33.65</v>
-      </c>
-      <c r="I6" s="8">
-        <v>16.97</v>
+        <v>9.01</v>
+      </c>
+      <c r="I6" s="21">
+        <v>4.54</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <v>-21.33</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <v>-25.14</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <v>0.98</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <v>3.81</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="21">
         <v>3.87</v>
       </c>
     </row>
@@ -1797,16 +1797,16 @@
         <v>-39.3</v>
       </c>
       <c r="F9" s="28">
-        <v>-49.47</v>
+        <v>-44.47</v>
       </c>
       <c r="G9" s="28">
         <v>2.65</v>
       </c>
       <c r="H9" s="28">
-        <v>10.17</v>
-      </c>
-      <c r="I9" s="24">
-        <v>3.84</v>
+        <v>5.17</v>
+      </c>
+      <c r="I9" s="21">
+        <v>1.95</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1826,16 +1826,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-49.47</v>
+        <v>-44.47</v>
       </c>
       <c r="G10" s="33">
         <v>7.88</v>
       </c>
       <c r="H10" s="33">
-        <v>74.11</v>
+        <v>44.47</v>
       </c>
       <c r="I10" s="33">
-        <v>9.4</v>
+        <v>5.64</v>
       </c>
     </row>
   </sheetData>
